--- a/i_test/test_D3_selezione_coorte/D3_OBSPERIODS.xlsx
+++ b/i_test/test_D3_selezione_coorte/D3_OBSPERIODS.xlsx
@@ -235,7 +235,7 @@
         <v>20120101</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>20171231</v>
+        <v>20251001</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -257,7 +257,7 @@
         <v>20120101</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>20181231</v>
+        <v>20251231</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -268,7 +268,7 @@
         <v>20120101</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>20181231</v>
+        <v>20251231</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
